--- a/검정도서_선정_평가표_3종.xlsx
+++ b/검정도서_선정_평가표_3종.xlsx
@@ -806,7 +806,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>표현·표기의 정확성 및 가독성</t>
+          <t>표현, 표기의 정확성 및 가독성</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -930,7 +930,7 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>동아출판㈜ 교과서는 교육과정 성취기준을 충실히 반영하면서도 학습 분량이 적절하여 한 학기 수업 운영에 무리가 없다 개념 도입 단계에서 실생활 소재를 활용하고 탐구 활동과 문제 해결 과정이 단계적으로 제시되어 학생 스스로 사고를 확장하기에 좋다 ㈜미래엔 교과서는 단원 간 연계가 매끄럽고 서술형 평가 문항이 풍부하며 ㈜비상교육 교과서는 편집이 깔끔하고 가독성이 높다 종합적으로 1순위 동아출판㈜, 2순위 ㈜미래엔, 3순위 ㈜비상교육을 추천함</t>
+          <t>동아출판㈜ 교과서는 교육과정 성취기준을 충실히 반영하면서도 학습 분량이 적절하여 한 학기 수업 운영에 무리가 없다. 개념 도입 단계에서 실생활 소재를 활용하고 탐구 활동과 문제 해결 과정이 단계적으로 제시되어 학생 스스로 사고를 확장하기에 좋다. ㈜미래엔 교과서는 단원 간 연계가 매끄럽고 서술형 평가 문항이 풍부하며 ㈜비상교육 교과서는 편집이 깔끔하고 가독성이 높다. 종합적으로 1순위 동아출판㈜, 2순위 ㈜미래엔, 3순위 ㈜비상교육을 추천함.</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>표현·표기의 정확성 및 가독성</t>
+          <t>표현, 표기의 정확성 및 가독성</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -1427,7 +1427,7 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>동아출판㈜ 교과서는 내용 수준이 우리 학교 학생들의 학력 분포에 가장 잘 맞고 기본 문제와 심화 문제의 난이도 배치가 균형적이다 공학적 도구 활용 활동과 협력 학습 과제가 구체적으로 안내되어 있어 학생 참여형 수업을 운영하기 쉽다 ㈜미래엔 교과서는 수학적 오개념을 짚어 주는 코너와 자기 평가 활동이 돋보이며 ㈜비상교육 교과서는 개념 정리와 예제 구성이 명확하다 따라서 1순위 동아출판㈜, 2순위 ㈜미래엔, 3순위 ㈜비상교육으로 추천함</t>
+          <t>동아출판㈜ 교과서는 내용 수준이 우리 학교 학생들의 학력 분포에 가장 잘 맞고 기본 문제와 심화 문제의 난이도 배치가 균형적이다. 공학적 도구 활용 활동과 협력 학습 과제가 구체적으로 안내되어 있어 학생 참여형 수업을 운영하기 쉽다. ㈜미래엔 교과서는 수학적 오개념을 짚어 주는 코너와 자기 평가 활동이 돋보이며 ㈜비상교육 교과서는 개념 정리와 예제 구성이 명확하다. 따라서 1순위 동아출판㈜, 2순위 ㈜미래엔, 3순위 ㈜비상교육으로 추천함.</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>표현·표기의 정확성 및 가독성</t>
+          <t>표현, 표기의 정확성 및 가독성</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -1924,7 +1924,7 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>동아출판㈜ 교과서는 이전 학년과의 계열성을 고려한 복습 코너와 다음 단원 예고가 잘 구성되어 학습의 흐름이 자연스럽다 용어와 기호 표기가 정확하고 삽화와 도표가 내용 이해를 돕도록 배치되어 있으며 가격 면에서도 부담이 적다 ㈜미래엔 교과서는 교수학습 자료와 디지털 연계 자료가 풍부하고 ㈜비상교육 교과서는 종합적 사고력을 요구하는 프로젝트 과제가 우수하다 이에 1순위 동아출판㈜, 2순위 ㈜미래엔, 3순위 ㈜비상교육을 추천함</t>
+          <t>동아출판㈜ 교과서는 이전 학년과의 계열성을 고려한 복습 코너와 다음 단원 예고가 잘 구성되어 학습의 흐름이 자연스럽다. 용어와 기호 표기가 정확하고 삽화와 도표가 내용 이해를 돕도록 배치되어 있으며 가격 면에서도 부담이 적다. ㈜미래엔 교과서는 교수학습 자료와 디지털 연계 자료가 풍부하고 ㈜비상교육 교과서는 종합적 사고력을 요구하는 프로젝트 과제가 우수하다. 이에 1순위 동아출판㈜, 2순위 ㈜미래엔, 3순위 ㈜비상교육을 추천함.</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>검·인정도서 선정기준 평가 총괄표</t>
+          <t>검인정도서 선정기준 평가 총괄표</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>추천 검·인정도서 및 추천 의견서</t>
+          <t>추천 검인정도서 및 추천 의견서</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>교육과정 성취기준을 충실히 반영하고 학습 분량과 내용 수준이 학생들의 학력 수준에 적합함 실생활 맥락의 도입 활동과 단계적 탐구 활동으로 개념을 자연스럽게 형성할 수 있으며 기본과 심화 문제의 난이도 배치가 균형적임 이전 학년과의 계열성을 고려한 단원 구성과 정확한 용어 및 기호 표기, 깔끔한 편집으로 가독성이 뛰어나 세 위원 모두 최고점을 부여하여 1순위로 추천함</t>
+          <t>교육과정 성취기준을 충실히 반영하고 학습 분량과 내용 수준이 학생들의 학력 수준에 적합함. 실생활 맥락의 도입 활동과 단계적 탐구 활동으로 개념을 자연스럽게 형성할 수 있으며 기본과 심화 문제의 난이도 배치가 균형적임. 이전 학년과의 계열성을 고려한 단원 구성과 정확한 용어 및 기호 표기, 깔끔한 편집으로 가독성이 뛰어나 세 위원 모두 최고점을 부여하여 1순위로 추천함.</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>단원 간 연계가 매끄럽고 수학적 오개념을 바로잡는 코너와 자기 평가 활동이 잘 갖추어져 있음 서술형 평가 문항과 교수학습 자료, 디지털 연계 자료가 풍부하여 다양한 수업 방법에 활용하기 좋으나 일부 단원의 학습 분량이 다소 많은 점을 고려하여 2순위로 추천함</t>
+          <t>단원 간 연계가 매끄럽고 수학적 오개념을 바로잡는 코너와 자기 평가 활동이 잘 갖추어져 있음. 서술형 평가 문항과 교수학습 자료, 디지털 연계 자료가 풍부하여 다양한 수업 방법에 활용하기 좋으나 일부 단원의 학습 분량이 다소 많은 점을 고려하여 2순위로 추천함.</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>개념 정리와 예제 구성이 명확하고 편집이 깔끔하여 학생들이 스스로 학습하기에 용이함 종합적 사고력을 요구하는 프로젝트 과제가 우수하나 학생 참여형 활동의 안내가 상대적으로 간략한 점을 고려하여 3순위로 추천함</t>
+          <t>개념 정리와 예제 구성이 명확하고 편집이 깔끔하여 학생들이 스스로 학습하기에 용이함. 종합적 사고력을 요구하는 프로젝트 과제가 우수하나 학생 참여형 활동의 안내가 상대적으로 간략한 점을 고려하여 3순위로 추천함.</t>
         </is>
       </c>
     </row>

--- a/검정도서_선정_평가표_3종.xlsx
+++ b/검정도서_선정_평가표_3종.xlsx
@@ -561,31 +561,31 @@
         <v>20</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>19</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K4" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="L4" s="3" t="n">
         <v>19</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -603,31 +603,31 @@
         <v>20</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="I5" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J5" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K5" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="K5" s="3" t="n">
-        <v>19</v>
-      </c>
       <c r="L5" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -645,31 +645,31 @@
         <v>10</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>9</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -687,16 +687,16 @@
         <v>10</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>9</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>8</v>
@@ -705,7 +705,7 @@
         <v>7</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>9</v>
@@ -735,16 +735,16 @@
         <v>10</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>8</v>
@@ -771,7 +771,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>10</v>
@@ -780,10 +780,10 @@
         <v>8</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>7</v>
@@ -795,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -813,28 +813,28 @@
         <v>10</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>7</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>9</v>
@@ -855,31 +855,31 @@
         <v>10</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -893,31 +893,31 @@
         <v>100</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -1061,28 +1061,28 @@
         <v>16</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>16</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I4" s="3" t="n">
         <v>15</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>14</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>15</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -1100,25 +1100,25 @@
         <v>20</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>19</v>
       </c>
       <c r="F5" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G5" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="H5" s="3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>18</v>
@@ -1142,25 +1142,25 @@
         <v>10</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>9</v>
@@ -1184,28 +1184,28 @@
         <v>10</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>9</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>8</v>
@@ -1226,28 +1226,28 @@
         <v>10</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>9</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>7</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>9</v>
@@ -1268,19 +1268,19 @@
         <v>10</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>9</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>8</v>
@@ -1289,7 +1289,7 @@
         <v>8</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>10</v>
@@ -1310,31 +1310,31 @@
         <v>10</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -1352,28 +1352,28 @@
         <v>10</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>9</v>
@@ -1390,28 +1390,28 @@
         <v>100</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>79</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>91</v>
@@ -1427,7 +1427,7 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>동아출판㈜ 교과서는 내용 수준이 우리 학교 학생들의 학력 분포에 가장 잘 맞고 기본 문제와 심화 문제의 난이도 배치가 균형적이다. 공학적 도구 활용 활동과 협력 학습 과제가 구체적으로 안내되어 있어 학생 참여형 수업을 운영하기 쉽다. ㈜미래엔 교과서는 수학적 오개념을 짚어 주는 코너와 자기 평가 활동이 돋보이며 ㈜비상교육 교과서는 개념 정리와 예제 구성이 명확하다. 따라서 1순위 동아출판㈜, 2순위 ㈜미래엔, 3순위 ㈜비상교육으로 추천함.</t>
+          <t>㈜미래엔 교과서는 수학적 오개념을 짚어 주는 코너와 자기 평가 활동이 돋보이고 교수학습 자료와 디지털 연계 자료가 풍부하여 수업 활용도가 높다. 동아출판㈜ 교과서는 내용 수준이 학생들의 학력 분포에 잘 맞고 기본 문제와 심화 문제의 난이도 배치가 균형적이다. ㈜비상교육 교과서는 개념 정리와 예제 구성이 명확하여 자기주도 학습에 도움이 된다. 따라서 1순위 ㈜미래엔, 2순위 동아출판㈜, 3순위 ㈜비상교육으로 추천함.</t>
         </is>
       </c>
     </row>
@@ -1555,31 +1555,31 @@
         <v>20</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>16</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -1597,7 +1597,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>20</v>
@@ -1606,22 +1606,22 @@
         <v>15</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -1645,25 +1645,25 @@
         <v>9</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -1681,22 +1681,22 @@
         <v>10</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>8</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>8</v>
@@ -1705,7 +1705,7 @@
         <v>9</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1723,31 +1723,31 @@
         <v>10</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>7</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -1771,25 +1771,25 @@
         <v>10</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>9</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -1810,25 +1810,25 @@
         <v>8</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="H10" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>9</v>
@@ -1849,31 +1849,31 @@
         <v>10</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="H11" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -1887,31 +1887,31 @@
         <v>100</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13">
@@ -1924,7 +1924,7 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>동아출판㈜ 교과서는 이전 학년과의 계열성을 고려한 복습 코너와 다음 단원 예고가 잘 구성되어 학습의 흐름이 자연스럽다. 용어와 기호 표기가 정확하고 삽화와 도표가 내용 이해를 돕도록 배치되어 있으며 가격 면에서도 부담이 적다. ㈜미래엔 교과서는 교수학습 자료와 디지털 연계 자료가 풍부하고 ㈜비상교육 교과서는 종합적 사고력을 요구하는 프로젝트 과제가 우수하다. 이에 1순위 동아출판㈜, 2순위 ㈜미래엔, 3순위 ㈜비상교육을 추천함.</t>
+          <t>동아출판㈜ 교과서는 이전 학년과의 계열성을 고려한 복습 코너와 다음 단원 예고가 잘 구성되어 학습의 흐름이 자연스럽고 가격 면에서도 부담이 적다. ㈜비상교육 교과서는 종합적 사고력을 요구하는 프로젝트 과제가 우수하고 삽화와 도표가 내용 이해를 돕도록 배치되어 있다. ㈜미래엔 교과서는 서술형 평가 문항이 풍부하나 일부 단원의 학습 분량이 다소 많다. 이에 1순위 동아출판㈜, 2순위 ㈜비상교육, 3순위 ㈜미래엔을 추천함.</t>
         </is>
       </c>
     </row>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>91</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>90.3</v>
+        <v>90</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -2041,19 +2041,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>196</v>
+        <v>242</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>65.3</v>
+        <v>80.7</v>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
     </row>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
+        <v>279</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>93</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>281</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>93.7</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -2091,19 +2091,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>73</v>
+        <v>80.3</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>79</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>79.3</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
     </row>
@@ -2137,19 +2137,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>74.3</v>
+        <v>79.7</v>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
     </row>
@@ -2160,19 +2160,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>85.7</v>
+        <v>89</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -2187,19 +2187,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>203</v>
+        <v>243</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>67.7</v>
+        <v>81</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
     </row>
@@ -2210,19 +2210,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>70.7</v>
+        <v>82.7</v>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>교육과정 성취기준을 충실히 반영하고 학습 분량과 내용 수준이 학생들의 학력 수준에 적합함. 실생활 맥락의 도입 활동과 단계적 탐구 활동으로 개념을 자연스럽게 형성할 수 있으며 기본과 심화 문제의 난이도 배치가 균형적임. 이전 학년과의 계열성을 고려한 단원 구성과 정확한 용어 및 기호 표기, 깔끔한 편집으로 가독성이 뛰어나 세 위원 모두 최고점을 부여하여 1순위로 추천함.</t>
+          <t>교육과정 성취기준을 충실히 반영하고 학습 분량과 내용 수준이 학생들의 학력 수준에 적합함. 실생활 맥락의 도입 활동과 단계적 탐구 활동으로 개념을 자연스럽게 형성할 수 있으며 기본과 심화 문제의 난이도 배치가 균형적임. 이전 학년과의 계열성을 고려한 단원 구성과 정확한 용어 및 기호 표기, 깔끔한 편집으로 가독성이 뛰어나 세 위원 합산 최고점을 받아 1순위로 추천함.</t>
         </is>
       </c>
     </row>
